--- a/data/기초자료_8차.xlsx
+++ b/data/기초자료_8차.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\5.배관투자\2026년_8차\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBB0067-E78F-47A6-B222-8FE35478BB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0241D0-6E0B-4DAF-8D53-2657798F98D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" tabRatio="706" xr2:uid="{0FA4570D-FA85-4B0E-B481-CED9CDCBBE83}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="706" xr2:uid="{0FA4570D-FA85-4B0E-B481-CED9CDCBBE83}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="149">
   <si>
     <t xml:space="preserve">  구간명</t>
   </si>
@@ -1512,310 +1512,307 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{399AC2EB-4F0F-4788-90B8-807E3DA5BAC3}">
-  <dimension ref="A1:BW22"/>
+  <dimension ref="A1:BV22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.125" customWidth="1"/>
     <col min="3" max="3" width="25.125" customWidth="1"/>
-    <col min="4" max="5" width="10.875" customWidth="1"/>
-    <col min="6" max="6" width="11.875" customWidth="1"/>
-    <col min="7" max="7" width="9" style="6"/>
-    <col min="8" max="8" width="14.75" style="6" customWidth="1"/>
-    <col min="69" max="70" width="13.75" style="6" customWidth="1"/>
+    <col min="4" max="4" width="10.875" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="9" style="6"/>
+    <col min="7" max="7" width="14.75" style="6" customWidth="1"/>
+    <col min="68" max="69" width="13.75" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:74" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="P1" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Y1" t="s">
         <v>7</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AA1" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AC1" t="s">
         <v>9</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AE1" t="s">
         <v>10</v>
       </c>
+      <c r="AG1" t="s">
+        <v>11</v>
+      </c>
       <c r="AH1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI1" t="s">
         <v>12</v>
       </c>
+      <c r="AS1" t="s">
+        <v>13</v>
+      </c>
       <c r="AT1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AU1" t="s">
         <v>14</v>
       </c>
+      <c r="AX1" t="s">
+        <v>15</v>
+      </c>
       <c r="AY1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AZ1" t="s">
         <v>16</v>
       </c>
+      <c r="BL1" t="s">
+        <v>17</v>
+      </c>
       <c r="BM1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BN1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BO1" t="s">
-        <v>19</v>
-      </c>
-      <c r="BP1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:74" x14ac:dyDescent="0.3">
+      <c r="F2" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="G2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
+      <c r="J2" t="s">
         <v>24</v>
       </c>
-      <c r="M2" t="s">
+      <c r="L2" t="s">
         <v>25</v>
       </c>
-      <c r="O2" t="s">
+      <c r="N2" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="P2" t="s">
         <v>27</v>
       </c>
-      <c r="S2" t="s">
+      <c r="R2" t="s">
         <v>28</v>
       </c>
-      <c r="U2" t="s">
+      <c r="T2" t="s">
         <v>29</v>
       </c>
-      <c r="W2" t="s">
+      <c r="V2" t="s">
         <v>30</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AH2" t="s">
         <v>31</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AK2" t="s">
         <v>32</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AY2" t="s">
         <v>33</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BB2" t="s">
         <v>34</v>
       </c>
+      <c r="BG2" t="s">
+        <v>35</v>
+      </c>
       <c r="BH2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BI2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BJ2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BK2" t="s">
-        <v>38</v>
-      </c>
-      <c r="BL2" t="s">
         <v>39</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BO2" t="s">
         <v>40</v>
       </c>
+      <c r="BP2" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="BQ2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="BR2" s="6" t="s">
         <v>42</v>
       </c>
+      <c r="BR2" t="s">
+        <v>43</v>
+      </c>
       <c r="BS2" t="s">
-        <v>43</v>
-      </c>
-      <c r="BT2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>128</v>
       </c>
       <c r="B4" t="s">
         <v>129</v>
       </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
       <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" t="s">
         <v>45</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>46</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>45</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>46</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
+        <v>47</v>
+      </c>
+      <c r="O4" t="s">
+        <v>48</v>
+      </c>
+      <c r="P4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U4" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" t="s">
+        <v>47</v>
+      </c>
+      <c r="W4" t="s">
+        <v>49</v>
+      </c>
+      <c r="X4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH4" t="s">
         <v>45</v>
       </c>
-      <c r="N4" t="s">
+      <c r="AI4" t="s">
         <v>46</v>
       </c>
-      <c r="O4" t="s">
-        <v>47</v>
-      </c>
-      <c r="P4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>47</v>
-      </c>
-      <c r="R4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S4" t="s">
-        <v>47</v>
-      </c>
-      <c r="T4" t="s">
-        <v>48</v>
-      </c>
-      <c r="U4" t="s">
-        <v>47</v>
-      </c>
-      <c r="V4" t="s">
-        <v>49</v>
-      </c>
-      <c r="W4" t="s">
-        <v>47</v>
-      </c>
-      <c r="X4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>45</v>
-      </c>
       <c r="AJ4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="AK4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AL4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AM4" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="AN4" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="AO4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AP4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AQ4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AR4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS4" t="s">
         <v>58</v>
       </c>
+      <c r="AT4" t="s">
+        <v>59</v>
+      </c>
       <c r="AU4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AV4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AW4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AX4" t="s">
         <v>62</v>
       </c>
+      <c r="AY4" t="s">
+        <v>63</v>
+      </c>
       <c r="AZ4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="BA4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="BB4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="BC4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="BD4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="BE4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="BF4" t="s">
-        <v>69</v>
-      </c>
-      <c r="BG4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>131</v>
       </c>
@@ -1825,27 +1822,27 @@
       <c r="C5" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="3">
-        <v>10011538</v>
+      <c r="D5" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F5" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="F5" s="7">
+        <v>4</v>
+      </c>
       <c r="G5" s="7">
-        <v>4</v>
-      </c>
-      <c r="H5" s="7">
         <v>38570000</v>
       </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4">
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
         <v>1336</v>
       </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
       <c r="K5" s="3">
         <v>0</v>
       </c>
@@ -1912,18 +1909,18 @@
       <c r="AF5" s="3">
         <v>0</v>
       </c>
-      <c r="AG5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="4">
+      <c r="AG5" s="4">
         <v>1336</v>
       </c>
-      <c r="AI5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="4">
+      <c r="AH5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="4">
         <v>5344</v>
       </c>
+      <c r="AJ5" s="3">
+        <v>0</v>
+      </c>
       <c r="AK5" s="3">
         <v>0</v>
       </c>
@@ -1948,33 +1945,33 @@
       <c r="AR5" s="3">
         <v>0</v>
       </c>
-      <c r="AS5" s="3">
-        <v>0</v>
+      <c r="AS5" s="4">
+        <v>5344</v>
       </c>
       <c r="AT5" s="4">
-        <v>5344</v>
-      </c>
-      <c r="AU5" s="4">
         <v>121469120</v>
       </c>
+      <c r="AU5" s="3">
+        <v>0</v>
+      </c>
       <c r="AV5" s="3">
         <v>0</v>
       </c>
-      <c r="AW5" s="3">
-        <v>0</v>
+      <c r="AW5" s="4">
+        <v>121469120</v>
       </c>
       <c r="AX5" s="4">
-        <v>121469120</v>
-      </c>
-      <c r="AY5" s="4">
         <v>-121469120</v>
       </c>
-      <c r="AZ5" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA5" s="4">
+      <c r="AY5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="4">
         <v>34981824</v>
       </c>
+      <c r="BA5" s="3">
+        <v>0</v>
+      </c>
       <c r="BB5" s="3">
         <v>0</v>
       </c>
@@ -2002,41 +1999,38 @@
       <c r="BJ5" s="3">
         <v>0</v>
       </c>
-      <c r="BK5" s="3">
-        <v>0</v>
+      <c r="BK5" s="4">
+        <v>34981824</v>
       </c>
       <c r="BL5" s="4">
-        <v>34981824</v>
+        <v>826833890</v>
       </c>
       <c r="BM5" s="4">
-        <v>826833890</v>
+        <v>729353539</v>
       </c>
       <c r="BN5" s="4">
-        <v>729353539</v>
-      </c>
-      <c r="BO5" s="4">
         <v>97480351</v>
       </c>
-      <c r="BP5" s="3">
+      <c r="BO5" s="3">
         <v>1</v>
       </c>
+      <c r="BP5" s="7">
+        <v>1059167435</v>
+      </c>
       <c r="BQ5" s="7">
-        <v>1059167435</v>
-      </c>
-      <c r="BR5" s="7">
         <v>210.09</v>
       </c>
-      <c r="BS5" s="5">
+      <c r="BR5" s="5">
         <v>33400</v>
       </c>
-      <c r="BT5" s="3">
-        <v>0</v>
-      </c>
+      <c r="BS5" s="3">
+        <v>0</v>
+      </c>
+      <c r="BT5" s="3"/>
       <c r="BU5" s="3"/>
       <c r="BV5" s="3"/>
-      <c r="BW5" s="3"/>
     </row>
-    <row r="6" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>131</v>
       </c>
@@ -2046,156 +2040,156 @@
       <c r="C6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="3">
-        <v>10011539</v>
+      <c r="D6" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F6" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="F6" s="7">
+        <v>7</v>
+      </c>
       <c r="G6" s="7">
-        <v>7</v>
-      </c>
-      <c r="H6" s="7">
         <v>21375000</v>
       </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
       <c r="I6" s="3">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="3">
         <v>168</v>
       </c>
-      <c r="K6" s="3">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="3">
-        <v>0</v>
-      </c>
       <c r="AH6" s="3">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3">
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="AJ6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="3">
         <v>672</v>
       </c>
-      <c r="AK6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT6" s="3">
-        <v>672</v>
-      </c>
-      <c r="AU6" s="4">
+      <c r="AT6" s="4">
         <v>15274560</v>
       </c>
+      <c r="AU6" s="3">
+        <v>0</v>
+      </c>
       <c r="AV6" s="3">
         <v>0</v>
       </c>
-      <c r="AW6" s="3">
-        <v>0</v>
+      <c r="AW6" s="4">
+        <v>15274560</v>
       </c>
       <c r="AX6" s="4">
-        <v>15274560</v>
-      </c>
-      <c r="AY6" s="4">
         <v>-15274560</v>
       </c>
-      <c r="AZ6" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA6" s="4">
+      <c r="AY6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="4">
         <v>4398912</v>
       </c>
+      <c r="BA6" s="3">
+        <v>0</v>
+      </c>
       <c r="BB6" s="3">
         <v>0</v>
       </c>
@@ -2223,41 +2217,38 @@
       <c r="BJ6" s="3">
         <v>0</v>
       </c>
-      <c r="BK6" s="3">
-        <v>0</v>
+      <c r="BK6" s="4">
+        <v>4398912</v>
       </c>
       <c r="BL6" s="4">
-        <v>4398912</v>
+        <v>103973123</v>
       </c>
       <c r="BM6" s="4">
-        <v>103973123</v>
+        <v>91715115</v>
       </c>
       <c r="BN6" s="4">
-        <v>91715115</v>
-      </c>
-      <c r="BO6" s="4">
         <v>12258008</v>
       </c>
-      <c r="BP6" s="3">
+      <c r="BO6" s="3">
         <v>3</v>
       </c>
+      <c r="BP6" s="7">
+        <v>116807028</v>
+      </c>
       <c r="BQ6" s="7">
-        <v>116807028</v>
-      </c>
-      <c r="BR6" s="7">
         <v>47.72</v>
       </c>
-      <c r="BS6" s="5">
+      <c r="BR6" s="5">
         <v>2400</v>
       </c>
-      <c r="BT6" s="3">
-        <v>0</v>
-      </c>
+      <c r="BS6" s="3">
+        <v>0</v>
+      </c>
+      <c r="BT6" s="3"/>
       <c r="BU6" s="3"/>
       <c r="BV6" s="3"/>
-      <c r="BW6" s="3"/>
     </row>
-    <row r="7" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -2267,218 +2258,215 @@
       <c r="C7" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="3">
-        <v>10011535</v>
+      <c r="D7" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F7" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="F7" s="7">
+        <v>1</v>
+      </c>
       <c r="G7" s="7">
+        <v>19743000</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1098</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="4">
+        <v>1098</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <v>4898</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <v>4898</v>
+      </c>
+      <c r="AT7" s="4">
+        <v>111331540</v>
+      </c>
+      <c r="AU7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="4">
+        <v>111331540</v>
+      </c>
+      <c r="AX7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="4">
+        <v>28750032</v>
+      </c>
+      <c r="BA7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BD7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BG7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BH7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BJ7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BK7" s="4">
+        <v>28750032</v>
+      </c>
+      <c r="BL7" s="4">
+        <v>679538631</v>
+      </c>
+      <c r="BM7" s="4">
+        <v>599423792</v>
+      </c>
+      <c r="BN7" s="4">
+        <v>80114839</v>
+      </c>
+      <c r="BO7" s="3">
         <v>1</v>
       </c>
-      <c r="H7" s="7">
-        <v>19743000</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4">
-        <v>1098</v>
-      </c>
-      <c r="K7" s="3">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3">
-        <v>0</v>
-      </c>
-      <c r="W7" s="3">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="4">
-        <v>1098</v>
-      </c>
-      <c r="AI7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="4">
-        <v>4898</v>
-      </c>
-      <c r="AK7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT7" s="4">
-        <v>4898</v>
-      </c>
-      <c r="AU7" s="4">
-        <v>111331540</v>
-      </c>
-      <c r="AV7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX7" s="4">
-        <v>111331540</v>
-      </c>
-      <c r="AY7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA7" s="4">
-        <v>28750032</v>
-      </c>
-      <c r="BB7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BE7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BG7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BH7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BI7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BJ7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BK7" s="3">
-        <v>0</v>
-      </c>
-      <c r="BL7" s="4">
-        <v>28750032</v>
-      </c>
-      <c r="BM7" s="4">
-        <v>679538631</v>
-      </c>
-      <c r="BN7" s="4">
-        <v>599423792</v>
-      </c>
-      <c r="BO7" s="4">
-        <v>80114839</v>
-      </c>
-      <c r="BP7" s="3">
-        <v>1</v>
-      </c>
-      <c r="BQ7" s="7">
+      <c r="BP7" s="7">
         <v>993110772</v>
       </c>
-      <c r="BR7" s="7" t="s">
+      <c r="BQ7" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="BS7" s="5">
+      <c r="BR7" s="5">
         <v>122450</v>
       </c>
-      <c r="BT7" s="3">
-        <v>0</v>
-      </c>
+      <c r="BS7" s="3">
+        <v>0</v>
+      </c>
+      <c r="BT7" s="3"/>
       <c r="BU7" s="3"/>
       <c r="BV7" s="3"/>
-      <c r="BW7" s="3"/>
     </row>
-    <row r="8" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -2488,21 +2476,21 @@
       <c r="C8" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D8" s="3">
-        <v>10011540</v>
+      <c r="D8" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F8" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="F8" s="7">
+        <v>7</v>
+      </c>
       <c r="G8" s="7">
-        <v>7</v>
-      </c>
-      <c r="H8" s="7">
         <v>18701000</v>
       </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
@@ -2531,29 +2519,29 @@
         <v>0</v>
       </c>
       <c r="R8" s="3">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3">
         <v>2</v>
       </c>
-      <c r="T8" s="4">
+      <c r="S8" s="4">
         <v>461052</v>
       </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>0</v>
-      </c>
-      <c r="W8" s="3">
         <v>1</v>
       </c>
+      <c r="W8" s="4">
+        <v>17765</v>
+      </c>
       <c r="X8" s="4">
-        <v>17765</v>
-      </c>
-      <c r="Y8" s="4">
         <v>22206</v>
       </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
@@ -2576,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="AG8" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH8" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3">
         <v>0</v>
@@ -2591,16 +2579,16 @@
         <v>0</v>
       </c>
       <c r="AL8" s="3">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="AM8" s="3">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="AN8" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO8" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AP8" s="3">
         <v>0</v>
@@ -2612,23 +2600,23 @@
         <v>0</v>
       </c>
       <c r="AS8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT8" s="3">
         <v>238</v>
       </c>
-      <c r="AU8" s="4">
+      <c r="AT8" s="4">
         <v>5409740</v>
       </c>
+      <c r="AU8" s="3">
+        <v>0</v>
+      </c>
       <c r="AV8" s="3">
         <v>0</v>
       </c>
-      <c r="AW8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX8" s="4">
+      <c r="AW8" s="4">
         <v>5409740</v>
       </c>
+      <c r="AX8" s="3">
+        <v>0</v>
+      </c>
       <c r="AY8" s="3">
         <v>0</v>
       </c>
@@ -2641,21 +2629,21 @@
       <c r="BB8" s="3">
         <v>0</v>
       </c>
-      <c r="BC8" s="3">
-        <v>0</v>
-      </c>
-      <c r="BD8" s="4">
+      <c r="BC8" s="4">
         <v>5532629</v>
       </c>
-      <c r="BE8" s="3">
-        <v>0</v>
+      <c r="BD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="4">
+        <v>213181</v>
       </c>
       <c r="BF8" s="4">
-        <v>213181</v>
-      </c>
-      <c r="BG8" s="4">
         <v>266477</v>
       </c>
+      <c r="BG8" s="3">
+        <v>0</v>
+      </c>
       <c r="BH8" s="3">
         <v>0</v>
       </c>
@@ -2665,41 +2653,38 @@
       <c r="BJ8" s="3">
         <v>0</v>
       </c>
-      <c r="BK8" s="3">
-        <v>0</v>
+      <c r="BK8" s="4">
+        <v>6012287</v>
       </c>
       <c r="BL8" s="4">
-        <v>6012287</v>
+        <v>134255717</v>
       </c>
       <c r="BM8" s="4">
-        <v>134255717</v>
+        <v>112408836</v>
       </c>
       <c r="BN8" s="4">
-        <v>112408836</v>
-      </c>
-      <c r="BO8" s="4">
         <v>21846881</v>
       </c>
-      <c r="BP8" s="3">
+      <c r="BO8" s="3">
         <v>1</v>
       </c>
+      <c r="BP8" s="7">
+        <v>217598615</v>
+      </c>
       <c r="BQ8" s="7">
-        <v>217598615</v>
-      </c>
-      <c r="BR8" s="7">
         <v>128.22999999999999</v>
       </c>
+      <c r="BR8" s="3">
+        <v>850</v>
+      </c>
       <c r="BS8" s="3">
-        <v>850</v>
-      </c>
-      <c r="BT8" s="3">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BT8" s="3"/>
       <c r="BU8" s="3"/>
       <c r="BV8" s="3"/>
-      <c r="BW8" s="3"/>
     </row>
-    <row r="9" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>130</v>
       </c>
@@ -2709,21 +2694,21 @@
       <c r="C9" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D9" s="3">
-        <v>10011514</v>
+      <c r="D9" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="F9" s="7">
+        <v>101</v>
+      </c>
       <c r="G9" s="7">
-        <v>101</v>
-      </c>
-      <c r="H9" s="7">
         <v>48672000</v>
       </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
       <c r="I9" s="3">
         <v>0</v>
       </c>
@@ -2731,10 +2716,10 @@
         <v>0</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L9" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3">
         <v>0</v>
@@ -2746,14 +2731,14 @@
         <v>0</v>
       </c>
       <c r="P9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3">
         <v>1</v>
       </c>
-      <c r="R9" s="4">
+      <c r="Q9" s="4">
         <v>23157</v>
       </c>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
       <c r="S9" s="3">
         <v>0</v>
       </c>
@@ -2797,22 +2782,22 @@
         <v>0</v>
       </c>
       <c r="AG9" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH9" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AJ9" s="3">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL9" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AM9" s="3">
         <v>0</v>
@@ -2833,38 +2818,38 @@
         <v>0</v>
       </c>
       <c r="AS9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT9" s="3">
         <v>92</v>
       </c>
-      <c r="AU9" s="4">
+      <c r="AT9" s="4">
         <v>2091160</v>
       </c>
-      <c r="AV9" s="3">
-        <v>0</v>
+      <c r="AU9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="4">
+        <v>3337024</v>
       </c>
       <c r="AW9" s="4">
-        <v>3337024</v>
-      </c>
-      <c r="AX9" s="4">
         <v>5428184</v>
       </c>
+      <c r="AX9" s="3">
+        <v>0</v>
+      </c>
       <c r="AY9" s="3">
         <v>0</v>
       </c>
-      <c r="AZ9" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA9" s="4">
+      <c r="AZ9" s="4">
         <v>529644</v>
       </c>
-      <c r="BB9" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC9" s="4">
+      <c r="BA9" s="3">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="4">
         <v>277885</v>
       </c>
+      <c r="BC9" s="3">
+        <v>0</v>
+      </c>
       <c r="BD9" s="3">
         <v>0</v>
       </c>
@@ -2886,41 +2871,38 @@
       <c r="BJ9" s="3">
         <v>0</v>
       </c>
-      <c r="BK9" s="3">
-        <v>0</v>
+      <c r="BK9" s="4">
+        <v>807529</v>
       </c>
       <c r="BL9" s="4">
-        <v>807529</v>
+        <v>18850072</v>
       </c>
       <c r="BM9" s="4">
-        <v>18850072</v>
+        <v>16347743</v>
       </c>
       <c r="BN9" s="4">
-        <v>16347743</v>
-      </c>
-      <c r="BO9" s="4">
         <v>2502329</v>
       </c>
-      <c r="BP9" s="3">
+      <c r="BO9" s="3">
         <v>31</v>
       </c>
+      <c r="BP9" s="7">
+        <v>-34405818</v>
+      </c>
       <c r="BQ9" s="7">
-        <v>-34405818</v>
-      </c>
-      <c r="BR9" s="7">
         <v>-4.5</v>
       </c>
+      <c r="BR9" s="3">
+        <v>22.8</v>
+      </c>
       <c r="BS9" s="3">
-        <v>22.8</v>
-      </c>
-      <c r="BT9" s="3">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BT9" s="3"/>
       <c r="BU9" s="3"/>
       <c r="BV9" s="3"/>
-      <c r="BW9" s="3"/>
     </row>
-    <row r="10" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>130</v>
       </c>
@@ -2930,21 +2912,21 @@
       <c r="C10" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="3">
-        <v>10011515</v>
+      <c r="D10" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F10" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="F10" s="7">
+        <v>98</v>
+      </c>
       <c r="G10" s="7">
-        <v>98</v>
-      </c>
-      <c r="H10" s="7">
         <v>66540000</v>
       </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
       <c r="I10" s="3">
         <v>0</v>
       </c>
@@ -2952,134 +2934,134 @@
         <v>0</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="3">
         <v>11</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3">
-        <v>0</v>
-      </c>
-      <c r="W10" s="3">
-        <v>0</v>
-      </c>
-      <c r="X10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>0</v>
-      </c>
       <c r="AH10" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="3">
         <v>44</v>
       </c>
-      <c r="AK10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT10" s="3">
-        <v>44</v>
-      </c>
-      <c r="AU10" s="4">
+      <c r="AT10" s="4">
         <v>1000120</v>
       </c>
-      <c r="AV10" s="3">
-        <v>0</v>
+      <c r="AU10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="4">
+        <v>7344920</v>
       </c>
       <c r="AW10" s="4">
-        <v>7344920</v>
-      </c>
-      <c r="AX10" s="4">
         <v>8345040</v>
       </c>
+      <c r="AX10" s="3">
+        <v>0</v>
+      </c>
       <c r="AY10" s="3">
         <v>0</v>
       </c>
-      <c r="AZ10" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA10" s="4">
+      <c r="AZ10" s="4">
         <v>306636</v>
       </c>
+      <c r="BA10" s="3">
+        <v>0</v>
+      </c>
       <c r="BB10" s="3">
         <v>0</v>
       </c>
@@ -3107,41 +3089,38 @@
       <c r="BJ10" s="3">
         <v>0</v>
       </c>
-      <c r="BK10" s="3">
-        <v>0</v>
+      <c r="BK10" s="4">
+        <v>306636</v>
       </c>
       <c r="BL10" s="4">
-        <v>306636</v>
+        <v>7247674</v>
       </c>
       <c r="BM10" s="4">
-        <v>7247674</v>
+        <v>6393203</v>
       </c>
       <c r="BN10" s="4">
-        <v>6393203</v>
-      </c>
-      <c r="BO10" s="4">
         <v>854471</v>
       </c>
-      <c r="BP10" s="3">
+      <c r="BO10" s="3">
         <v>31</v>
       </c>
+      <c r="BP10" s="7">
+        <v>-64624451</v>
+      </c>
       <c r="BQ10" s="7">
-        <v>-64624451</v>
-      </c>
-      <c r="BR10" s="7">
         <v>-999.99</v>
       </c>
+      <c r="BR10" s="3">
+        <v>11.2</v>
+      </c>
       <c r="BS10" s="3">
-        <v>11.2</v>
-      </c>
-      <c r="BT10" s="3">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BT10" s="3"/>
       <c r="BU10" s="3"/>
       <c r="BV10" s="3"/>
-      <c r="BW10" s="3"/>
     </row>
-    <row r="11" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>130</v>
       </c>
@@ -3151,21 +3130,21 @@
       <c r="C11" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="3">
-        <v>10011518</v>
+      <c r="D11" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="F11" s="7">
+        <v>179</v>
+      </c>
       <c r="G11" s="7">
-        <v>179</v>
-      </c>
-      <c r="H11" s="7">
         <v>83659000</v>
       </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
       <c r="I11" s="3">
         <v>0</v>
       </c>
@@ -3173,134 +3152,134 @@
         <v>0</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0</v>
+      </c>
+      <c r="R11" s="3">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3">
+        <v>0</v>
+      </c>
+      <c r="V11" s="3">
+        <v>0</v>
+      </c>
+      <c r="W11" s="3">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="3">
         <v>28</v>
       </c>
-      <c r="M11" s="3">
-        <v>0</v>
-      </c>
-      <c r="N11" s="3">
-        <v>0</v>
-      </c>
-      <c r="O11" s="3">
-        <v>0</v>
-      </c>
-      <c r="P11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3">
-        <v>0</v>
-      </c>
-      <c r="S11" s="3">
-        <v>0</v>
-      </c>
-      <c r="T11" s="3">
-        <v>0</v>
-      </c>
-      <c r="U11" s="3">
-        <v>0</v>
-      </c>
-      <c r="V11" s="3">
-        <v>0</v>
-      </c>
-      <c r="W11" s="3">
-        <v>0</v>
-      </c>
-      <c r="X11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="3">
-        <v>0</v>
-      </c>
       <c r="AH11" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="AJ11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="3">
         <v>112</v>
       </c>
-      <c r="AK11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT11" s="3">
-        <v>112</v>
-      </c>
-      <c r="AU11" s="4">
+      <c r="AT11" s="4">
         <v>2545760</v>
       </c>
-      <c r="AV11" s="3">
-        <v>0</v>
+      <c r="AU11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="4">
+        <v>10867584</v>
       </c>
       <c r="AW11" s="4">
-        <v>10867584</v>
-      </c>
-      <c r="AX11" s="4">
         <v>13413344</v>
       </c>
+      <c r="AX11" s="3">
+        <v>0</v>
+      </c>
       <c r="AY11" s="3">
         <v>0</v>
       </c>
-      <c r="AZ11" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA11" s="4">
+      <c r="AZ11" s="4">
         <v>780528</v>
       </c>
+      <c r="BA11" s="3">
+        <v>0</v>
+      </c>
       <c r="BB11" s="3">
         <v>0</v>
       </c>
@@ -3328,41 +3307,38 @@
       <c r="BJ11" s="3">
         <v>0</v>
       </c>
-      <c r="BK11" s="3">
-        <v>0</v>
+      <c r="BK11" s="4">
+        <v>780528</v>
       </c>
       <c r="BL11" s="4">
-        <v>780528</v>
+        <v>18448625</v>
       </c>
       <c r="BM11" s="4">
-        <v>18448625</v>
+        <v>16273610</v>
       </c>
       <c r="BN11" s="4">
-        <v>16273610</v>
-      </c>
-      <c r="BO11" s="4">
         <v>2175015</v>
       </c>
-      <c r="BP11" s="3">
+      <c r="BO11" s="3">
         <v>31</v>
       </c>
+      <c r="BP11" s="7">
+        <v>-78877699</v>
+      </c>
       <c r="BQ11" s="7">
-        <v>-78877699</v>
-      </c>
-      <c r="BR11" s="7">
         <v>-999.99</v>
       </c>
+      <c r="BR11" s="3">
+        <v>15.6</v>
+      </c>
       <c r="BS11" s="3">
-        <v>15.6</v>
-      </c>
-      <c r="BT11" s="3">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BT11" s="3"/>
       <c r="BU11" s="3"/>
       <c r="BV11" s="3"/>
-      <c r="BW11" s="3"/>
     </row>
-    <row r="12" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>130</v>
       </c>
@@ -3372,21 +3348,21 @@
       <c r="C12" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D12" s="3">
-        <v>10011521</v>
+      <c r="D12" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F12" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="F12" s="7">
+        <v>38</v>
+      </c>
       <c r="G12" s="7">
-        <v>38</v>
-      </c>
-      <c r="H12" s="7">
         <v>31540000</v>
       </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
       <c r="I12" s="3">
         <v>0</v>
       </c>
@@ -3394,134 +3370,134 @@
         <v>0</v>
       </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="3">
         <v>3</v>
       </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3">
-        <v>0</v>
-      </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
-      <c r="S12" s="3">
-        <v>0</v>
-      </c>
-      <c r="T12" s="3">
-        <v>0</v>
-      </c>
-      <c r="U12" s="3">
-        <v>0</v>
-      </c>
-      <c r="V12" s="3">
-        <v>0</v>
-      </c>
-      <c r="W12" s="3">
-        <v>0</v>
-      </c>
-      <c r="X12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>0</v>
-      </c>
       <c r="AH12" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AJ12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="3">
         <v>14</v>
       </c>
-      <c r="AK12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT12" s="3">
-        <v>14</v>
-      </c>
-      <c r="AU12" s="4">
+      <c r="AT12" s="4">
         <v>318220</v>
       </c>
-      <c r="AV12" s="3">
-        <v>0</v>
+      <c r="AU12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="4">
+        <v>3210270</v>
       </c>
       <c r="AW12" s="4">
-        <v>3210270</v>
-      </c>
-      <c r="AX12" s="4">
         <v>3528490</v>
       </c>
+      <c r="AX12" s="3">
+        <v>0</v>
+      </c>
       <c r="AY12" s="3">
         <v>0</v>
       </c>
-      <c r="AZ12" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA12" s="4">
+      <c r="AZ12" s="4">
         <v>83628</v>
       </c>
+      <c r="BA12" s="3">
+        <v>0</v>
+      </c>
       <c r="BB12" s="3">
         <v>0</v>
       </c>
@@ -3549,41 +3525,38 @@
       <c r="BJ12" s="3">
         <v>0</v>
       </c>
-      <c r="BK12" s="3">
-        <v>0</v>
+      <c r="BK12" s="4">
+        <v>83628</v>
       </c>
       <c r="BL12" s="4">
-        <v>83628</v>
+        <v>1976638</v>
       </c>
       <c r="BM12" s="4">
-        <v>1976638</v>
+        <v>1743601</v>
       </c>
       <c r="BN12" s="4">
-        <v>1743601</v>
-      </c>
-      <c r="BO12" s="4">
         <v>233037</v>
       </c>
-      <c r="BP12" s="3">
+      <c r="BO12" s="3">
         <v>31</v>
       </c>
+      <c r="BP12" s="7">
+        <v>-31034409</v>
+      </c>
       <c r="BQ12" s="7">
-        <v>-31034409</v>
-      </c>
-      <c r="BR12" s="7">
         <v>-999.99</v>
       </c>
+      <c r="BR12" s="3">
+        <v>9.1999999999999993</v>
+      </c>
       <c r="BS12" s="3">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="BT12" s="3">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BT12" s="3"/>
       <c r="BU12" s="3"/>
       <c r="BV12" s="3"/>
-      <c r="BW12" s="3"/>
     </row>
-    <row r="13" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>130</v>
       </c>
@@ -3593,21 +3566,21 @@
       <c r="C13" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="3">
-        <v>10011536</v>
+      <c r="D13" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F13" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="F13" s="7">
+        <v>33</v>
+      </c>
       <c r="G13" s="7">
-        <v>33</v>
-      </c>
-      <c r="H13" s="7">
         <v>29189000</v>
       </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
       <c r="I13" s="3">
         <v>0</v>
       </c>
@@ -3615,134 +3588,134 @@
         <v>0</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
         <v>8</v>
       </c>
-      <c r="M13" s="3">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3">
-        <v>0</v>
-      </c>
-      <c r="O13" s="3">
-        <v>0</v>
-      </c>
-      <c r="P13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>0</v>
-      </c>
-      <c r="R13" s="3">
-        <v>0</v>
-      </c>
-      <c r="S13" s="3">
-        <v>0</v>
-      </c>
-      <c r="T13" s="3">
-        <v>0</v>
-      </c>
-      <c r="U13" s="3">
-        <v>0</v>
-      </c>
-      <c r="V13" s="3">
-        <v>0</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0</v>
-      </c>
-      <c r="X13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="3">
-        <v>0</v>
-      </c>
       <c r="AH13" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="3">
         <v>32</v>
       </c>
-      <c r="AK13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT13" s="3">
-        <v>32</v>
-      </c>
-      <c r="AU13" s="4">
+      <c r="AT13" s="4">
         <v>727360</v>
       </c>
-      <c r="AV13" s="3">
-        <v>0</v>
+      <c r="AU13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="4">
+        <v>3089152</v>
       </c>
       <c r="AW13" s="4">
-        <v>3089152</v>
-      </c>
-      <c r="AX13" s="4">
         <v>3816512</v>
       </c>
+      <c r="AX13" s="3">
+        <v>0</v>
+      </c>
       <c r="AY13" s="3">
         <v>0</v>
       </c>
-      <c r="AZ13" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA13" s="4">
+      <c r="AZ13" s="4">
         <v>223008</v>
       </c>
+      <c r="BA13" s="3">
+        <v>0</v>
+      </c>
       <c r="BB13" s="3">
         <v>0</v>
       </c>
@@ -3770,41 +3743,38 @@
       <c r="BJ13" s="3">
         <v>0</v>
       </c>
-      <c r="BK13" s="3">
-        <v>0</v>
+      <c r="BK13" s="4">
+        <v>223008</v>
       </c>
       <c r="BL13" s="4">
-        <v>223008</v>
+        <v>5271034</v>
       </c>
       <c r="BM13" s="4">
-        <v>5271034</v>
+        <v>4649602</v>
       </c>
       <c r="BN13" s="4">
-        <v>4649602</v>
-      </c>
-      <c r="BO13" s="4">
         <v>621432</v>
       </c>
-      <c r="BP13" s="3">
+      <c r="BO13" s="3">
         <v>31</v>
       </c>
+      <c r="BP13" s="7">
+        <v>-23129282</v>
+      </c>
       <c r="BQ13" s="7">
-        <v>-23129282</v>
-      </c>
-      <c r="BR13" s="7">
         <v>-8.39</v>
       </c>
+      <c r="BR13" s="3">
+        <v>15.7</v>
+      </c>
       <c r="BS13" s="3">
-        <v>15.7</v>
-      </c>
-      <c r="BT13" s="3">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BT13" s="3"/>
       <c r="BU13" s="3"/>
       <c r="BV13" s="3"/>
-      <c r="BW13" s="3"/>
     </row>
-    <row r="14" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>130</v>
       </c>
@@ -3814,21 +3784,21 @@
       <c r="C14" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="3">
-        <v>10011537</v>
+      <c r="D14" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F14" s="3" t="s">
         <v>78</v>
       </c>
+      <c r="F14" s="7">
+        <v>120</v>
+      </c>
       <c r="G14" s="7">
-        <v>120</v>
-      </c>
-      <c r="H14" s="7">
         <v>70883000</v>
       </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
@@ -3836,134 +3806,134 @@
         <v>0</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>25</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="3">
         <v>100</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AU14" s="4">
+      <c r="AT14" s="4">
         <v>2273000</v>
       </c>
-      <c r="AV14" s="3">
-        <v>0</v>
+      <c r="AU14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="4">
+        <v>8945200</v>
       </c>
       <c r="AW14" s="4">
-        <v>8945200</v>
-      </c>
-      <c r="AX14" s="4">
         <v>11218200</v>
       </c>
+      <c r="AX14" s="3">
+        <v>0</v>
+      </c>
       <c r="AY14" s="3">
         <v>0</v>
       </c>
-      <c r="AZ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="BA14" s="4">
+      <c r="AZ14" s="4">
         <v>696900</v>
       </c>
+      <c r="BA14" s="3">
+        <v>0</v>
+      </c>
       <c r="BB14" s="3">
         <v>0</v>
       </c>
@@ -3991,174 +3961,171 @@
       <c r="BJ14" s="3">
         <v>0</v>
       </c>
-      <c r="BK14" s="3">
-        <v>0</v>
+      <c r="BK14" s="4">
+        <v>696900</v>
       </c>
       <c r="BL14" s="4">
-        <v>696900</v>
+        <v>16471981</v>
       </c>
       <c r="BM14" s="4">
-        <v>16471981</v>
+        <v>14530004</v>
       </c>
       <c r="BN14" s="4">
-        <v>14530004</v>
-      </c>
-      <c r="BO14" s="4">
         <v>1941977</v>
       </c>
-      <c r="BP14" s="3">
+      <c r="BO14" s="3">
         <v>31</v>
       </c>
+      <c r="BP14" s="7">
+        <v>-58566588</v>
+      </c>
       <c r="BQ14" s="7">
-        <v>-58566588</v>
-      </c>
-      <c r="BR14" s="7">
         <v>-14.43</v>
       </c>
+      <c r="BR14" s="3">
+        <v>16.3</v>
+      </c>
       <c r="BS14" s="3">
-        <v>16.3</v>
-      </c>
-      <c r="BT14" s="3">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BT14" s="3"/>
       <c r="BU14" s="3"/>
       <c r="BV14" s="3"/>
-      <c r="BW14" s="3"/>
     </row>
-    <row r="17" spans="6:70" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:69" x14ac:dyDescent="0.3">
+      <c r="F17" s="6">
+        <f>SUM(F5:F14)</f>
+        <v>588</v>
+      </c>
       <c r="G17" s="6">
         <f>SUM(G5:G14)</f>
-        <v>588</v>
-      </c>
-      <c r="H17" s="6">
-        <f>SUM(H5:H14)</f>
         <v>428872000</v>
+      </c>
+      <c r="BP17" s="6">
+        <f>SUM(BP5:BP14)</f>
+        <v>2096045603</v>
       </c>
       <c r="BQ17" s="6">
         <f>SUM(BQ5:BQ14)</f>
-        <v>2096045603</v>
-      </c>
-      <c r="BR17" s="6">
-        <f>SUM(BR5:BR14)</f>
         <v>-2641.25</v>
       </c>
     </row>
-    <row r="18" spans="6:70" x14ac:dyDescent="0.3">
-      <c r="F18" t="s">
+    <row r="18" spans="5:69" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
         <v>131</v>
+      </c>
+      <c r="F18" s="6">
+        <f>SUM(F5:F7)</f>
+        <v>12</v>
       </c>
       <c r="G18" s="6">
         <f>SUM(G5:G7)</f>
-        <v>12</v>
-      </c>
-      <c r="H18" s="6">
-        <f>SUM(H5:H7)</f>
         <v>79688000</v>
       </c>
-      <c r="BP18" t="s">
+      <c r="BO18" t="s">
         <v>131</v>
+      </c>
+      <c r="BP18" s="6">
+        <f>SUM(BP5:BP7)</f>
+        <v>2169085235</v>
       </c>
       <c r="BQ18" s="6">
         <f>SUM(BQ5:BQ7)</f>
-        <v>2169085235</v>
-      </c>
-      <c r="BR18" s="6">
-        <f>SUM(BR5:BR7)</f>
         <v>257.81</v>
       </c>
     </row>
-    <row r="19" spans="6:70" x14ac:dyDescent="0.3">
-      <c r="F19" t="s">
+    <row r="19" spans="5:69" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
         <v>132</v>
+      </c>
+      <c r="F19" s="6">
+        <f>F8</f>
+        <v>7</v>
       </c>
       <c r="G19" s="6">
         <f>G8</f>
-        <v>7</v>
-      </c>
-      <c r="H19" s="6">
-        <f>H8</f>
         <v>18701000</v>
       </c>
-      <c r="BP19" t="s">
+      <c r="BO19" t="s">
         <v>132</v>
+      </c>
+      <c r="BP19" s="6">
+        <f>BP8</f>
+        <v>217598615</v>
       </c>
       <c r="BQ19" s="6">
         <f>BQ8</f>
-        <v>217598615</v>
-      </c>
-      <c r="BR19" s="6">
-        <f>BR8</f>
         <v>128.22999999999999</v>
       </c>
     </row>
-    <row r="20" spans="6:70" x14ac:dyDescent="0.3">
-      <c r="F20" t="s">
+    <row r="20" spans="5:69" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
         <v>130</v>
+      </c>
+      <c r="F20" s="6">
+        <f>SUM(F9:F14)</f>
+        <v>569</v>
       </c>
       <c r="G20" s="6">
         <f>SUM(G9:G14)</f>
-        <v>569</v>
-      </c>
-      <c r="H20" s="6">
-        <f>SUM(H9:H14)</f>
         <v>330483000</v>
       </c>
-      <c r="BP20" t="s">
+      <c r="BO20" t="s">
         <v>130</v>
+      </c>
+      <c r="BP20" s="6">
+        <f>SUM(BP9:BP14)</f>
+        <v>-290638247</v>
       </c>
       <c r="BQ20" s="6">
         <f>SUM(BQ9:BQ14)</f>
-        <v>-290638247</v>
-      </c>
-      <c r="BR20" s="6">
-        <f>SUM(BR9:BR14)</f>
         <v>-3027.29</v>
       </c>
     </row>
-    <row r="21" spans="6:70" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:69" x14ac:dyDescent="0.3">
+      <c r="F21" s="6">
+        <f>SUM(F18:F20)</f>
+        <v>588</v>
+      </c>
       <c r="G21" s="6">
         <f>SUM(G18:G20)</f>
-        <v>588</v>
-      </c>
-      <c r="H21" s="6">
-        <f>SUM(H18:H20)</f>
         <v>428872000</v>
+      </c>
+      <c r="BP21" s="6">
+        <f>SUM(BP18:BP20)</f>
+        <v>2096045603</v>
       </c>
       <c r="BQ21" s="6">
         <f>SUM(BQ18:BQ20)</f>
-        <v>2096045603</v>
-      </c>
-      <c r="BR21" s="6">
-        <f>SUM(BR18:BR20)</f>
         <v>-2641.25</v>
       </c>
     </row>
-    <row r="22" spans="6:70" x14ac:dyDescent="0.3">
-      <c r="F22" s="8" t="s">
+    <row r="22" spans="5:69" x14ac:dyDescent="0.3">
+      <c r="E22" s="8" t="s">
         <v>140</v>
+      </c>
+      <c r="F22" s="9">
+        <f>F17-F20</f>
+        <v>19</v>
       </c>
       <c r="G22" s="9">
         <f>G17-G20</f>
-        <v>19</v>
-      </c>
-      <c r="H22" s="9">
-        <f>H17-H20</f>
         <v>98389000</v>
       </c>
-      <c r="BP22" t="s">
+      <c r="BO22" t="s">
         <v>140</v>
+      </c>
+      <c r="BP22" s="6">
+        <f>BP17-BP20</f>
+        <v>2386683850</v>
       </c>
       <c r="BQ22" s="6">
         <f>BQ17-BQ20</f>
-        <v>2386683850</v>
-      </c>
-      <c r="BR22" s="6">
-        <f>BR17-BR20</f>
         <v>386.03999999999996</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:BV14">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:BU14">
     <sortCondition descending="1" ref="A5:A14"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
